--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1488</v>
+        <v>1446</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -13340,14 +13340,14 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
         <v>83113000</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>55856</v>
+        <v>57478</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>83113000</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>55856</v>
+        <v>57478</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1602</v>
+        <v>1559</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -13402,14 +13402,14 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
         <v>94598000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>59050</v>
+        <v>60679</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>94598000</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>59050</v>
+        <v>60679</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -26918,18 +26918,18 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1602呎 (4+房)
+          <t>A | 1559呎 (4+房)
 $9460万
-$59,050/呎
-(26年-08月-19日)</t>
+$60,679/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1488呎 (4+房)
+          <t>B | 1446呎 (4+房)
 $8311万
-$55,856/呎
-(26年-08月-19日)</t>
+$57,478/呎
+(26年-09月-11日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2086</v>
+        <v>2134</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2031</v>
+        <v>2083</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>153036000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>75350</v>
+        <v>73469</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>153036000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>75350</v>
+        <v>73469</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>62280000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>55164</v>
+        <v>53095</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>62280000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>55164</v>
+        <v>53095</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1540</v>
+        <v>1585</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>99350000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>64513</v>
+        <v>62681</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>99350000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>64513</v>
+        <v>62681</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1540</v>
+        <v>1585</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>81982000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>53235</v>
+        <v>51724</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>81982000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>53235</v>
+        <v>51724</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1524</v>
+        <v>1568</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>83888000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>55045</v>
+        <v>53500</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>83888000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>55045</v>
+        <v>53500</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2322</v>
+        <v>2373</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>200000000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>86133</v>
+        <v>84282</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>200000000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>86133</v>
+        <v>84282</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1555</v>
+        <v>1599</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>109000000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>70096</v>
+        <v>68168</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>109000000</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>70096</v>
+        <v>68168</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1555</v>
+        <v>1599</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>100055450</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>64344</v>
+        <v>62574</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>100055450</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>64344</v>
+        <v>62574</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1423</v>
+        <v>1467</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>78522000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>55181</v>
+        <v>53526</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>78522000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>55181</v>
+        <v>53526</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1423</v>
+        <v>1467</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>76284000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>53608</v>
+        <v>52000</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>76284000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>53608</v>
+        <v>52000</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1423</v>
+        <v>1467</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>14290200</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>10042</v>
+        <v>9741</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>14290200</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>10042</v>
+        <v>9741</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1485</v>
+        <v>1530</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>98485000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>66320</v>
+        <v>64369</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>98485000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>66320</v>
+        <v>64369</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1973</v>
+        <v>2023</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>59388800</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>40789</v>
+        <v>39619</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>59388800</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>40789</v>
+        <v>39619</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>1129</v>
+        <v>1173</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1456</v>
+        <v>1499</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>73912000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>50764</v>
+        <v>49308</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>73912000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>50764</v>
+        <v>49308</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>43605000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>57075</v>
+        <v>57000</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>43605000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>57075</v>
+        <v>57000</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>13291200</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>34977</v>
+        <v>35069</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>13291200</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>34977</v>
+        <v>35069</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>13205400</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>34751</v>
+        <v>34843</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>13205400</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>34751</v>
+        <v>34843</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>13656600</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>35938</v>
+        <v>36033</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>13656600</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>35938</v>
+        <v>36033</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>13389300</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>35235</v>
+        <v>35328</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>13389300</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>35235</v>
+        <v>35328</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>12997200</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>34203</v>
+        <v>34293</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>12997200</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>34203</v>
+        <v>34293</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>13059600</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>34367</v>
+        <v>34458</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>13059600</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>34367</v>
+        <v>34458</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>12772000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>33611</v>
+        <v>33699</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>12772000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>33611</v>
+        <v>33699</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>13762000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>36216</v>
+        <v>36311</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>13762000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>36216</v>
+        <v>36311</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>14076500</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>37043</v>
+        <v>37141</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>14076500</v>
       </c>
       <c r="L158" s="5" t="n">
-        <v>37043</v>
+        <v>37141</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>12896800</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>33939</v>
+        <v>34028</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>12896800</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>33939</v>
+        <v>34028</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>12612500</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>33191</v>
+        <v>33278</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>12612500</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>33191</v>
+        <v>33278</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>12581700</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>33110</v>
+        <v>33197</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>12581700</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>33110</v>
+        <v>33197</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>68270000</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>47213</v>
+        <v>45880</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>68270000</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>47213</v>
+        <v>45880</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>81406000</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>52217</v>
+        <v>50815</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>81406000</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>52217</v>
+        <v>50815</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>83113000</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>57478</v>
+        <v>55856</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>83113000</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>57478</v>
+        <v>55856</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>94598000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>60679</v>
+        <v>59050</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>94598000</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>60679</v>
+        <v>59050</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>66067200</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>45690</v>
+        <v>44400</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>66067200</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>45690</v>
+        <v>44400</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>64962500</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>44926</v>
+        <v>43658</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>64962500</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>44926</v>
+        <v>43658</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>80990000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>51950</v>
+        <v>50556</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>80990000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>51950</v>
+        <v>50556</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>63860000</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>44163</v>
+        <v>42917</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>63860000</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>44163</v>
+        <v>42917</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>86187000</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>55284</v>
+        <v>53800</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>86187000</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>55284</v>
+        <v>53800</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>62793600</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>43426</v>
+        <v>42200</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>62793600</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>43426</v>
+        <v>42200</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>72090000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>46241</v>
+        <v>45000</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>72090000</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>46241</v>
+        <v>45000</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         </is>
       </c>
       <c r="E208" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>61730000</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>42690</v>
+        <v>41485</v>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>61730000</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>42690</v>
+        <v>41485</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>70167600</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>45008</v>
+        <v>43800</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>70167600</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>45008</v>
+        <v>43800</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>60717840</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>41990</v>
+        <v>40805</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>60717840</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>41990</v>
+        <v>40805</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>68245200</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>43775</v>
+        <v>42600</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>68245200</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>43775</v>
+        <v>42600</v>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>1446</v>
+        <v>1488</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>73656000</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>50938</v>
+        <v>49500</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>73656000</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>50938</v>
+        <v>49500</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>66322800</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>42542</v>
+        <v>41400</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>66322800</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>42542</v>
+        <v>41400</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         </is>
       </c>
       <c r="E215" s="4" t="n">
-        <v>1559</v>
+        <v>1602</v>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>64720000</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>41514</v>
+        <v>40400</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>64720000</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>41514</v>
+        <v>40400</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2086呎 (4+房)
+          <t>A | 2134呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -24412,9 +24412,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2031呎 (4+房)
+          <t>A | 2083呎 (4+房)
 $15304万
-$75,350/呎
+$73,469/呎
 (20年-01月-22日)</t>
         </is>
       </c>
@@ -24551,9 +24551,9 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 $6228万
-$55,164/呎
+$53,095/呎
 (19年-08月-21日)</t>
         </is>
       </c>
@@ -24566,9 +24566,9 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 1540呎 (4+房)
+          <t>A | 1585呎 (4+房)
 $9935万
-$64,513/呎
+$62,681/呎
 (18年-05月-17日)</t>
         </is>
       </c>
@@ -24589,9 +24589,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1540呎 (4+房)
+          <t>A | 1585呎 (4+房)
 $8198万
-$53,235/呎
+$51,724/呎
 (18年-06月-06日)</t>
         </is>
       </c>
@@ -24658,9 +24658,9 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 1524呎 (4+房)
+          <t>A | 1568呎 (4+房)
 $8389万
-$55,045/呎
+$53,500/呎
 (21年-03月-31日)</t>
         </is>
       </c>
@@ -24808,9 +24808,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2322呎 (4+房)
+          <t>A | 2373呎 (4+房)
 $20000万
-$86,133/呎
+$84,282/呎
 (26年-07月-20日)</t>
         </is>
       </c>
@@ -24824,9 +24824,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1555呎 (4+房)
+          <t>A | 1599呎 (4+房)
 $10900万
-$70,096/呎
+$68,168/呎
 (21年-11月-19日)</t>
         </is>
       </c>
@@ -24870,9 +24870,9 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1555呎 (4+房)
+          <t>A | 1599呎 (4+房)
 $10006万
-$64,344/呎
+$62,574/呎
 (18年-08月-06日)</t>
         </is>
       </c>
@@ -24924,9 +24924,9 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 1423呎 (4+房)
+          <t>B | 1467呎 (4+房)
 $7852万
-$55,181/呎
+$53,526/呎
 (18年-06月-21日)</t>
         </is>
       </c>
@@ -24970,9 +24970,9 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1423呎 (4+房)
+          <t>B | 1467呎 (4+房)
 $7628万
-$53,608/呎
+$52,000/呎
 (21年-12月-09日)</t>
         </is>
       </c>
@@ -24993,9 +24993,9 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 1423呎 (4+房)
+          <t>B | 1467呎 (4+房)
 $1429万
-$10,042/呎
+$9,741/呎
 (19年-01月-09日)</t>
         </is>
       </c>
@@ -25100,9 +25100,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 1485呎 (4+房)
+          <t>A | 1530呎 (4+房)
 $9848万
-$66,320/呎
+$64,369/呎
 (21年-05月-05日)</t>
         </is>
       </c>
@@ -25250,7 +25250,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>A | 1973呎 (4+房)
+          <t>A | 2023呎 (4+房)
 -
 -
 (待售)</t>
@@ -25266,7 +25266,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25297,7 +25297,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25320,7 +25320,7 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25335,15 +25335,15 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 $5939万
-$40,789/呎
+$39,619/呎
 (24年-10月-08日)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25358,7 +25358,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25366,7 +25366,7 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25389,7 +25389,7 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25435,7 +25435,7 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25450,7 +25450,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25458,7 +25458,7 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25496,7 +25496,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25504,7 +25504,7 @@
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25542,7 +25542,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 -
 -
 (待售)</t>
@@ -25550,7 +25550,7 @@
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25565,15 +25565,15 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>A | 1456呎 (4+房)
+          <t>A | 1499呎 (4+房)
 $7391万
-$50,764/呎
+$49,308/呎
 (18年-06月-11日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>B | 1129呎 (3房)
+          <t>B | 1173呎 (3房)
 -
 -
 (待售)</t>
@@ -25746,9 +25746,9 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 764呎 (2房)
+          <t>A | 765呎 (2房)
 $4360万
-$57,075/呎
+$57,000/呎
 (23年-03月-10日)</t>
         </is>
       </c>
@@ -25804,9 +25804,9 @@
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1329万
-$34,977/呎
+$35,069/呎
 (18年-08月-08日)</t>
         </is>
       </c>
@@ -25859,9 +25859,9 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1321万
-$34,751/呎
+$34,843/呎
 (18年-08月-03日)</t>
         </is>
       </c>
@@ -25914,9 +25914,9 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1366万
-$35,938/呎
+$36,033/呎
 (19年-07月-05日)</t>
         </is>
       </c>
@@ -25969,9 +25969,9 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1339万
-$35,235/呎
+$35,328/呎
 (18年-08月-10日)</t>
         </is>
       </c>
@@ -26024,9 +26024,9 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1300万
-$34,203/呎
+$34,293/呎
 (18年-08月-01日)</t>
         </is>
       </c>
@@ -26244,9 +26244,9 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1306万
-$34,367/呎
+$34,458/呎
 (18年-08月-09日)</t>
         </is>
       </c>
@@ -26299,9 +26299,9 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1277万
-$33,611/呎
+$33,699/呎
 (18年-08月-08日)</t>
         </is>
       </c>
@@ -26354,9 +26354,9 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1376万
-$36,216/呎
+$36,311/呎
 (18年-08月-08日)</t>
         </is>
       </c>
@@ -26409,9 +26409,9 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1408万
-$37,043/呎
+$37,141/呎
 (18年-08月-06日)</t>
         </is>
       </c>
@@ -26519,9 +26519,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1290万
-$33,939/呎
+$34,028/呎
 (18年-08月-10日)</t>
         </is>
       </c>
@@ -26574,9 +26574,9 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1261万
-$33,191/呎
+$33,278/呎
 (18年-08月-06日)</t>
         </is>
       </c>
@@ -26629,9 +26629,9 @@
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>D | 380呎 (1房)
+          <t>D | 379呎 (1房)
 $1258万
-$33,110/呎
+$33,197/呎
 (18年-08月-06日)</t>
         </is>
       </c>
@@ -26895,17 +26895,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $8141万
-$52,217/呎
+$50,815/呎
 (25年-09月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6827万
-$47,213/呎
+$45,880/呎
 (25年-06月-16日)</t>
         </is>
       </c>
@@ -26918,17 +26918,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $9460万
-$60,679/呎
+$59,050/呎
 (26年-09月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $8311万
-$57,478/呎
+$55,856/呎
 (26年-09月-11日)</t>
         </is>
       </c>
@@ -26949,9 +26949,9 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6607万
-$45,690/呎
+$44,400/呎
 (25年-08月-04日)</t>
         </is>
       </c>
@@ -26964,17 +26964,17 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $8099万
-$51,950/呎
+$50,556/呎
 (25年-12月-15日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6496万
-$44,926/呎
+$43,658/呎
 (25年-07月-24日)</t>
         </is>
       </c>
@@ -26987,17 +26987,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $8619万
-$55,284/呎
+$53,800/呎
 (23年-12月-14日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6386万
-$44,163/呎
+$42,917/呎
 (25年-06月-17日)</t>
         </is>
       </c>
@@ -27010,17 +27010,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $7209万
-$46,241/呎
+$45,000/呎
 (25年-11月-11日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6279万
-$43,426/呎
+$42,200/呎
 (25年-10月-13日)</t>
         </is>
       </c>
@@ -27033,17 +27033,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $7017万
-$45,008/呎
+$43,800/呎
 (25年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6173万
-$42,690/呎
+$41,485/呎
 (25年-10月-30日)</t>
         </is>
       </c>
@@ -27056,17 +27056,17 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $6825万
-$43,775/呎
+$42,600/呎
 (25年-10月-21日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $6072万
-$41,990/呎
+$40,805/呎
 (25年-12月-02日)</t>
         </is>
       </c>
@@ -27079,17 +27079,17 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $6632万
-$42,542/呎
+$41,400/呎
 (25年-06月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>B | 1446呎 (4+房)
+          <t>B | 1488呎 (4+房)
 $7366万
-$50,938/呎
+$49,500/呎
 (26年-08月-25日)</t>
         </is>
       </c>
@@ -27102,9 +27102,9 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>A | 1559呎 (4+房)
+          <t>A | 1602呎 (4+房)
 $6472万
-$41,514/呎
+$40,400/呎
 (25年-08月-08日)</t>
         </is>
       </c>
